--- a/trust/CodeSystem-Participants-DEV.xlsx
+++ b/trust/CodeSystem-Participants-DEV.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.0</t>
+    <t>1.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-27T08:38:34+00:00</t>
+    <t>2026-02-11T14:17:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/trust/CodeSystem-Participants-DEV.xlsx
+++ b/trust/CodeSystem-Participants-DEV.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.4.0</t>
+    <t>1.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T14:17:30+00:00</t>
+    <t>2026-04-27T07:32:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/trust/CodeSystem-Participants-DEV.xlsx
+++ b/trust/CodeSystem-Participants-DEV.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.5.0</t>
+    <t>1.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-27T07:32:49+00:00</t>
+    <t>2026-07-03T08:24:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/trust/CodeSystem-Participants-DEV.xlsx
+++ b/trust/CodeSystem-Participants-DEV.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-03T08:24:29+00:00</t>
+    <t>2026-07-06T11:52:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/trust/CodeSystem-Participants-DEV.xlsx
+++ b/trust/CodeSystem-Participants-DEV.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.6.0</t>
+    <t>1.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T11:52:41+00:00</t>
+    <t>2026-07-30T11:57:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/trust/CodeSystem-Participants-DEV.xlsx
+++ b/trust/CodeSystem-Participants-DEV.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="82">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.7.0</t>
+    <t>1.7.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T11:57:48+00:00</t>
+    <t>2026-08-27T05:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -123,7 +123,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>20</t>
+    <t>25</t>
   </si>
   <si>
     <t>Level</t>
@@ -141,75 +141,66 @@
     <t>1</t>
   </si>
   <si>
+    <t>IOM</t>
+  </si>
+  <si>
+    <t>TEST</t>
+  </si>
+  <si>
     <t>DEV Participant WHO</t>
   </si>
   <si>
     <t>XCL</t>
   </si>
   <si>
-    <t>DEV Participant XCL</t>
+    <t>California</t>
   </si>
   <si>
     <t>XML</t>
   </si>
   <si>
-    <t>DEV Participant XML</t>
+    <t>GDHCN entomo</t>
   </si>
   <si>
     <t>XXA</t>
   </si>
   <si>
-    <t>DEV Participant XXA</t>
+    <t>Geneva</t>
   </si>
   <si>
     <t>XXB</t>
   </si>
   <si>
-    <t>DEV Participant XXB</t>
-  </si>
-  <si>
     <t>XXC</t>
   </si>
   <si>
-    <t>DEV Participant XXC</t>
-  </si>
-  <si>
     <t>XXD</t>
   </si>
   <si>
-    <t>DEV Participant XXD</t>
+    <t>CENS XD</t>
   </si>
   <si>
     <t>XXE</t>
   </si>
   <si>
-    <t>DEV Participant XXE</t>
+    <t>Geneva XE</t>
   </si>
   <si>
     <t>XXF</t>
   </si>
   <si>
-    <t>DEV Participant XXF</t>
+    <t>Test Locality XF</t>
   </si>
   <si>
     <t>XXG</t>
   </si>
   <si>
-    <t>DEV Participant XXG</t>
-  </si>
-  <si>
     <t>XXH</t>
   </si>
   <si>
-    <t>DEV Participant XXH</t>
-  </si>
-  <si>
     <t>XXI</t>
   </si>
   <si>
-    <t>DEV Participant XXI</t>
-  </si>
-  <si>
     <t>XXJ</t>
   </si>
   <si>
@@ -219,7 +210,13 @@
     <t>XXK</t>
   </si>
   <si>
-    <t>DEV Participant XXK</t>
+    <t>Rengo</t>
+  </si>
+  <si>
+    <t>XXN</t>
+  </si>
+  <si>
+    <t>DEV Participant XXN</t>
   </si>
   <si>
     <t>XXO</t>
@@ -231,31 +228,37 @@
     <t>XXP</t>
   </si>
   <si>
-    <t>DEV Participant XXP</t>
+    <t>XXQ</t>
+  </si>
+  <si>
+    <t>Test Locality</t>
+  </si>
+  <si>
+    <t>XXT</t>
   </si>
   <si>
     <t>XXU</t>
   </si>
   <si>
-    <t>DEV Participant XXU</t>
-  </si>
-  <si>
     <t>XXV</t>
   </si>
   <si>
-    <t>DEV Participant XXV</t>
+    <t>test city</t>
+  </si>
+  <si>
+    <t>XXW</t>
   </si>
   <si>
     <t>XXX</t>
   </si>
   <si>
-    <t>DEV Participant XXX</t>
+    <t>Warrandyte</t>
   </si>
   <si>
     <t>XYK</t>
   </si>
   <si>
-    <t>DEV Participant XYK</t>
+    <t>Test</t>
   </si>
 </sst>
 </file>
@@ -565,7 +568,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -587,10 +590,10 @@
         <v>41</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D2" s="2"/>
     </row>
@@ -599,7 +602,7 @@
         <v>41</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s" s="2">
         <v>44</v>
@@ -650,7 +653,7 @@
         <v>51</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D7" s="2"/>
     </row>
@@ -659,10 +662,10 @@
         <v>41</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="D8" s="2"/>
     </row>
@@ -671,10 +674,10 @@
         <v>41</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D9" s="2"/>
     </row>
@@ -683,10 +686,10 @@
         <v>41</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D10" s="2"/>
     </row>
@@ -695,10 +698,10 @@
         <v>41</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D11" s="2"/>
     </row>
@@ -707,10 +710,10 @@
         <v>41</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="D12" s="2"/>
     </row>
@@ -719,10 +722,10 @@
         <v>41</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="D13" s="2"/>
     </row>
@@ -731,10 +734,10 @@
         <v>41</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="D14" s="2"/>
     </row>
@@ -743,10 +746,10 @@
         <v>41</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D15" s="2"/>
     </row>
@@ -755,10 +758,10 @@
         <v>41</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D16" s="2"/>
     </row>
@@ -767,10 +770,10 @@
         <v>41</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D17" s="2"/>
     </row>
@@ -779,10 +782,10 @@
         <v>41</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D18" s="2"/>
     </row>
@@ -791,10 +794,10 @@
         <v>41</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="D19" s="2"/>
     </row>
@@ -803,10 +806,10 @@
         <v>41</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D20" s="2"/>
     </row>
@@ -815,12 +818,72 @@
         <v>41</v>
       </c>
       <c r="B21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="D21" s="2"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="D22" s="2"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="D23" s="2"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="D24" s="2"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="C25" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="C21" t="s" s="2">
+      <c r="D25" s="2"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="D21" s="2"/>
+      <c r="C26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="D26" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/trust/CodeSystem-Participants-DEV.xlsx
+++ b/trust/CodeSystem-Participants-DEV.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.7.1</t>
+    <t>1.7.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T05:52:17+00:00</t>
+    <t>2026-09-03T12:39:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
